--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_los_rios_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_los_rios_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 23:16</t>
+    <t xml:space="preserve">2026-09-29 14:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_los_rios_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_los_rios_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 14:05</t>
+    <t xml:space="preserve">2026-09-29 18:44</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -487,10 +487,10 @@
         <v>23.54</v>
       </c>
       <c r="C2" s="2" t="n">
-        <v>79.31</v>
+        <v>79.32</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>55.77</v>
+        <v>55.78</v>
       </c>
     </row>
     <row r="3">
@@ -504,7 +504,7 @@
         <v>56.83</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>37.18</v>
+        <v>37.19</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_los_rios_provincial.xlsx
+++ b/output/graficos_regionales_migracion/plot_migracion_miginterna_2022_los_rios_provincial.xlsx
@@ -46,7 +46,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 18:44</t>
+    <t xml:space="preserve">2026-10-05 04:09</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -501,7 +501,7 @@
         <v>19.65</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>56.83</v>
+        <v>56.84</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>37.19</v>
